--- a/p6_deployment/data/england/predicciones.xlsx
+++ b/p6_deployment/data/england/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,100 +460,110 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>odds_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>odds_draw</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>odds_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_home_bm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_draw_bm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_away_bm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>predicted_result</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_class_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>copiado_formaciones</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -562,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jXP8f29S</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45431.5</v>
+        <v>45520.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>arsenal</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>everton</t>
+          <t>fulham</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -584,84 +594,96 @@
       <c r="F2" t="n">
         <v>481</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7.5</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>1.53</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7784120394395433</v>
+        <v>4.33</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1266216917488324</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09496626881162429</v>
+        <v>0.6217557060086298</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0530054644808744</v>
+        <v>0.2196965889591694</v>
       </c>
       <c r="N2" t="n">
+        <v>0.1585477050322006</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05120832012558685</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>0.5692431075905363</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.3072278436644664</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0.1235290487449972</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>0.587546288237472</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.2880536949448699</v>
+      </c>
       <c r="S2" t="n">
-        <v>-0.209168931849007</v>
+        <v>0.1244000168176581</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.209168931849007</v>
+        <v>-0.03420941777115782</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5692431075905363</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X2" t="inlineStr">
+        <v>-0.03420941777115782</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.587546288237472</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>28.46215537952682</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>28.46215537952682</v>
+      <c r="AA2" t="n">
+        <v>41.12824017662304</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>41.12824017662304</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>htCzjMHq</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45431.5</v>
+        <v>45521.35416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>brentford</t>
+          <t>ipswich</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>newcastle</t>
+          <t>liverpool</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -670,84 +692,96 @@
       <c r="F3" t="n">
         <v>481</v>
       </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I3" t="n">
-        <v>2.15</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3179297597042514</v>
+        <v>5.25</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2384473197781886</v>
+        <v>1.36</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4436229205175601</v>
+        <v>0.1336828309305373</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04844961240310064</v>
+        <v>0.1782437745740498</v>
       </c>
       <c r="N3" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.06862745098039214</v>
+      </c>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.2528775569205888</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.3690718364094134</v>
-      </c>
       <c r="Q3" t="n">
-        <v>0.3780506066699977</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>0.2033009276898471</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.3060257948368023</v>
+      </c>
       <c r="S3" t="n">
-        <v>-0.0655723138475624</v>
+        <v>0.4906732774733504</v>
       </c>
       <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.1974001170220624</v>
+      </c>
+      <c r="V3" t="n">
         <v>2</v>
       </c>
-      <c r="U3" t="n">
-        <v>-0.0655723138475624</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.3780506066699977</v>
-      </c>
       <c r="W3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X3" t="inlineStr">
+        <v>-0.1974001170220624</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4906732774733504</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>18.90253033349989</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>18.90253033349989</v>
+      <c r="AA3" t="n">
+        <v>34.34712942313453</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>34.34712942313453</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45431.5</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brighton</t>
+          <t>arsenal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>wolves</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -756,84 +790,96 @@
       <c r="F4" t="n">
         <v>481</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I4" t="n">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3886084388989428</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2380226688256024</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3733688922754549</v>
+        <v>0.7784120394395433</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05032012805122044</v>
+        <v>0.1582771146860404</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.06331084587441618</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1618264580042491</v>
+        <v>0.0530054644808744</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4667726176291225</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3714009243666285</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>0.4449947492484919</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3116895454487841</v>
+      </c>
       <c r="S4" t="n">
-        <v>0.22874994880352</v>
+        <v>0.2433157053027239</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.22874994880352</v>
+        <v>-0.3334172901910514</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4667726176291225</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
-      </c>
-      <c r="X4" t="inlineStr">
+        <v>-0.3334172901910514</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4449947492484919</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>23.33863088145612</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>23.33863088145612</v>
+      <c r="AA4" t="n">
+        <v>31.14963244739443</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>31.14963244739443</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45431.5</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>burnley</t>
+          <t>everton</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nottingham</t>
+          <t>brighton</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -842,84 +888,96 @@
       <c r="F5" t="n">
         <v>481</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.75</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3311067603362892</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2542899919382701</v>
+        <v>2.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4146032477254405</v>
+        <v>0.3947157726180945</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04867149758454126</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="O5" t="n">
-        <v>0.277942704979128</v>
+        <v>0.05561189993238669</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3695877002500257</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3524695947708462</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>0.2321192511673387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3650135583525272</v>
+      </c>
       <c r="S5" t="n">
-        <v>0.1152977083117556</v>
+        <v>0.4028671904801341</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1152977083117556</v>
+        <v>0.07620586141688346</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3695877002500257</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X5" t="inlineStr">
+        <v>0.07620586141688346</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4028671904801341</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y5" t="n">
-        <v>18.47938501250129</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18.47938501250129</v>
+      <c r="AA5" t="n">
+        <v>28.20070333360939</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>28.20070333360939</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45431.5</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>newcastle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bournemouth</t>
+          <t>southampton</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -928,84 +986,96 @@
       <c r="F6" t="n">
         <v>481</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.25</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I6" t="n">
-        <v>6.25</v>
+        <v>1.36</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6677010734089638</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1805972427125197</v>
+        <v>8.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1517016838785165</v>
+        <v>0.6983240223463686</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05470154258886661</v>
+        <v>0.1899441340782123</v>
       </c>
       <c r="N6" t="n">
+        <v>0.111731843575419</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05294117647058827</v>
+      </c>
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.3978644444078878</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.3219983223643792</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.280137233227733</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>0.4646862712823306</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.35636760501756</v>
+      </c>
       <c r="S6" t="n">
-        <v>-0.269836629001076</v>
+        <v>0.1789461237001093</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.269836629001076</v>
+        <v>-0.2336377510640379</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3978644444078878</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X6" t="inlineStr">
+        <v>-0.2336377510640379</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4646862712823306</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y6" t="n">
-        <v>19.89322222039439</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>19.89322222039439</v>
+      <c r="AA6" t="n">
+        <v>32.52803898976315</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>32.52803898976315</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45431.5</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>crystal palace</t>
+          <t>nottingham</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>aston villa</t>
+          <t>bournemouth</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1014,84 +1084,96 @@
       <c r="F7" t="n">
         <v>481</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.33</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I7" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5645371577574968</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2177314211212516</v>
+        <v>2.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2177314211212516</v>
+        <v>0.3741092636579573</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06069615964376096</v>
+        <v>0.2725653206650831</v>
       </c>
       <c r="N7" t="n">
+        <v>0.3533254156769596</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04824151882975425</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="n">
-        <v>0.3156260766311601</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.3939815295323135</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.2903923938365265</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>0.3104057318093947</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3805739284238408</v>
+      </c>
       <c r="S7" t="n">
-        <v>0.1762501084110619</v>
+        <v>0.3090203397667642</v>
       </c>
       <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1080086077587577</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="n">
-        <v>0.1762501084110619</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.3939815295323135</v>
-      </c>
       <c r="W7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X7" t="inlineStr">
+        <v>0.1080086077587577</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.3805739284238408</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y7" t="n">
-        <v>19.69907647661568</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>19.69907647661568</v>
+      <c r="AA7" t="n">
+        <v>26.64017498966886</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>26.64017498966886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45431.5</v>
+        <v>45521.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>liverpool</t>
+          <t>west ham</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>wolves</t>
+          <t>aston villa</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1100,84 +1182,96 @@
       <c r="F8" t="n">
         <v>481</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8377135348226018</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1061103810775295</v>
+        <v>2.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05617608409986859</v>
+        <v>0.3645833333333334</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04712762297901629</v>
+        <v>0.2708333333333334</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.3645833333333334</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4636488693376835</v>
+        <v>0.05494505494505475</v>
       </c>
       <c r="P8" t="n">
-        <v>0.307873101779956</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2284780288823605</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <v>0.3535423482744904</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3934948385053813</v>
+      </c>
       <c r="S8" t="n">
-        <v>-0.3740646654849183</v>
+        <v>0.2529628132201283</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3740646654849183</v>
+        <v>0.1226615051720479</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4636488693376835</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="inlineStr">
+        <v>0.1226615051720479</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.3934948385053813</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y8" t="n">
-        <v>23.18244346688417</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>23.18244346688417</v>
+      <c r="AA8" t="n">
+        <v>27.54463869537669</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>27.54463869537669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45431.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>luton</t>
+          <t>brentford</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>fulham</t>
+          <t>crystal palace</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1186,237 +1280,3013 @@
       <c r="F9" t="n">
         <v>481</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.9</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3266082984392844</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2428625808907499</v>
+        <v>2.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4305291206699657</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05578329716260755</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="N9" t="n">
+        <v>0.3371104815864023</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05942376950780304</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
-        <v>0.2449029764296939</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.4084598004037597</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.3466372231665464</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>0.3054699661287714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3865281173371165</v>
+      </c>
       <c r="S9" t="n">
-        <v>0.1655972195130098</v>
+        <v>0.3080019165341121</v>
       </c>
       <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1089077207365499</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="n">
-        <v>0.1655972195130098</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.4084598004037597</v>
-      </c>
       <c r="W9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X9" t="inlineStr">
+        <v>0.1089077207365499</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3865281173371165</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y9" t="n">
-        <v>20.42299002018799</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20.42299002018799</v>
+      <c r="AA9" t="n">
+        <v>27.05696821359815</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>27.05696821359815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45431.5</v>
+        <v>45514.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>manchester utd</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>manchester city</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>west ham</t>
-        </is>
-      </c>
       <c r="E10" t="n">
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>481</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H10" t="n">
-        <v>15</v>
+        <v>482</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>fa community shield</t>
+        </is>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>5.75</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8910386965376781</v>
+        <v>5.25</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06356076035302104</v>
+        <v>1.42</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04540054310930074</v>
+        <v>0.1627462751732795</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04886515353805088</v>
+        <v>0.1782459204278775</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0.659007804398843</v>
       </c>
       <c r="O10" t="n">
-        <v>0.535960716870522</v>
+        <v>0.06861458606712745</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2990525105901231</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1649867725393549</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>0.3092592671082137</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.335971774796851</v>
+      </c>
       <c r="S10" t="n">
-        <v>-0.355077979667156</v>
+        <v>0.3547689580949353</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.355077979667156</v>
+        <v>-0.3042388463039077</v>
       </c>
       <c r="V10" t="n">
-        <v>0.535960716870522</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X10" t="inlineStr">
+        <v>-0.3042388463039077</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.3547689580949353</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y10" t="n">
-        <v>26.7980358435261</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>26.7980358435261</v>
+      <c r="AA10" t="n">
+        <v>24.83382706664547</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24.83382706664547</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45431.5</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>stoke</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>484</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1877107530910453</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2502810041213938</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.562008242787561</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06546906187624746</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>1.251874062968516</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>leyton orient</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>newport</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="n">
+        <v>484</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6106870229007634</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.233587786259542</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1557251908396947</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0702614379084967</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>1.219123505976096</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>stockport county</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>blackburn</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>484</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06448801742919397</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>1.298076923076923</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>barrow</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>port vale</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>484</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3765084473049075</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2614641995172969</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3620273531777956</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06239316239316239</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>1.274509803921569</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bolton</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mansfield</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>484</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5653773669568339</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2248048101947411</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.209817822848425</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05911985552704113</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>1.217990275526742</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bristol city</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>coventry</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>484</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3620273531777956</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2614641995172969</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3765084473049075</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06239316239316239</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4879081638868339</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.273786198928091</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.238305637185075</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1258808107090383</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1258808107090383</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.4879081638868339</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>34.15357147207837</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>34.15357147207837</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bromley</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>afc wimbledon</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>484</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3231597845601437</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2603231597845602</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4165170556552962</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06704980842911867</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>1.266990291262136</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>burton</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>blackpool</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>484</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3234659870613605</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2501470299941188</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4263869829445207</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06603970741901777</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>1.250980392156863</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cambridge utd</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>qpr</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" t="n">
+        <v>484</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>1.271451876019576</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cardiff</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>bristol rovers</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>484</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5791912384161751</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2502106149957877</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1705981465880371</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06576879910213251</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>1.251404494382022</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>charlton</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>birmingham</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>484</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3039936419630439</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2771706735545401</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.418835684482416</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06114273666455827</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>1.303738317757009</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>colchester</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>48</v>
+      </c>
+      <c r="F22" t="n">
+        <v>484</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>1.271451876019576</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>crawley</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>swindon</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>48</v>
+      </c>
+      <c r="F23" t="n">
+        <v>484</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.06442577030812324</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>1.298181818181818</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>derby</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>chesterfield</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>48</v>
+      </c>
+      <c r="F24" t="n">
+        <v>484</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5977796754910334</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2681468830059778</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.1340734415029889</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.06551410373066413</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>1.282380396732789</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>fleetwood</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>west brom</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>48</v>
+      </c>
+      <c r="F25" t="n">
+        <v>484</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1705981465880371</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.2502106149957877</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5791912384161753</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.06576879910213229</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>1.251404494382022</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>grimsby</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>bradford city</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>48</v>
+      </c>
+      <c r="F26" t="n">
+        <v>484</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2765957446808511</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.06334841628959276</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>huddersfield</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>morecambe</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>48</v>
+      </c>
+      <c r="F27" t="n">
+        <v>484</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.595120015869867</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.249156913310851</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.1557230708192819</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0702760084925691</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>1.244385733157199</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>lincoln</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>harrogate</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>48</v>
+      </c>
+      <c r="F28" t="n">
+        <v>484</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6297577854671281</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2249134948096886</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.1453287197231834</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0586080586080584</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>1.21875</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>northampton</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>wycombe</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>48</v>
+      </c>
+      <c r="F29" t="n">
+        <v>484</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.3958218801539307</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.2770753161077515</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.3271028037383177</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.06150793650793651</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>1.303117870722433</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>norwich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>stevenage</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>48</v>
+      </c>
+      <c r="F30" t="n">
+        <v>484</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6264014466546112</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.1566003616636528</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oxford utd</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>peterborough</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>48</v>
+      </c>
+      <c r="F31" t="n">
+        <v>484</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.4165170556552962</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.2603231597845602</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.3231597845601437</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.06704980842911867</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>1.266990291262136</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>portsmouth</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>millwall</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>48</v>
+      </c>
+      <c r="F32" t="n">
+        <v>484</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3774574049803408</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2948885976408912</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.327653997378768</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.05972222222222223</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="n">
+        <v>1.338289962825279</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>preston</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sunderland</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>48</v>
+      </c>
+      <c r="F33" t="n">
+        <v>484</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.3958218801539307</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2770753161077515</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.3271028037383177</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.06150793650793651</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.3904461185194874</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.3346801439734999</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2748737375070125</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-0.005375761634443366</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-0.005375761634443366</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.3904461185194874</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>27.33122829636411</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>27.33122829636411</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rotherham</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>crewe</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>48</v>
+      </c>
+      <c r="F34" t="n">
+        <v>484</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5816922989614663</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2298393961750184</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.1884683048635151</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.06118638964167422</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="n">
+        <v>1.22356495468278</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>salford</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>doncaster</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>48</v>
+      </c>
+      <c r="F35" t="n">
+        <v>484</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.4102564102564102</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.2621082621082621</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.3276353276353276</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.05978260869565233</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="n">
+        <v>1.278764478764479</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>shrewsbury</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>notts co</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>48</v>
+      </c>
+      <c r="F36" t="n">
+        <v>484</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.4093097913322633</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.2768860353130017</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.3138041733547351</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.06223358908780896</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="n">
+        <v>1.30188679245283</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>swansea</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>gillingham</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>48</v>
+      </c>
+      <c r="F37" t="n">
+        <v>484</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.6264014466546112</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1566003616636528</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>tranmere</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>accrington</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>48</v>
+      </c>
+      <c r="F38" t="n">
+        <v>484</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.4485336400230017</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.261644623346751</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.2898217366302473</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.06166056166056166</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="n">
+        <v>1.275700934579439</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>walsall</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>exeter</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>48</v>
+      </c>
+      <c r="F39" t="n">
+        <v>484</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.2611940298507463</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.4701492537313433</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>watford</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>mk dons</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>48</v>
+      </c>
+      <c r="F40" t="n">
+        <v>484</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.6264014466546112</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1566003616636528</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>wigan</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>barnsley</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>48</v>
+      </c>
+      <c r="F41" t="n">
+        <v>484</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.418835684482416</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.2771706735545401</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.3039936419630439</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.06114273666455827</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="n">
+        <v>1.303738317757009</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45517.66666666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>sheffield utd</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>tottenham</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>48</v>
-      </c>
-      <c r="F11" t="n">
-        <v>481</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.1336800244723157</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1627408993576017</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7035790761700825</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.06864988558352403</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.09377537066634738</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.3890028153921654</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.5172218139414873</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>-0.1863572622285953</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.1863572622285953</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.5172218139414873</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>wrexham</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>48</v>
+      </c>
+      <c r="F42" t="n">
+        <v>484</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.5993833395353783</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.2295199617245229</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.1710966987400989</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.06266329600180764</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="n">
+        <v>1.221357850070721</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>hull</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sheffield wed</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>48</v>
+      </c>
+      <c r="F43" t="n">
+        <v>484</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.4903728275762602</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.2754741472560756</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.2341530251676643</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.06767785648290725</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.4576062362731794</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.3133115276720925</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.2290822360547282</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-0.03276659130308085</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-0.03276659130308085</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.4576062362731794</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z43" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y11" t="n">
-        <v>25.86109069707436</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>25.86109069707436</v>
+      <c r="AA43" t="n">
+        <v>32.03243653912256</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>32.03243653912256</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>plymouth</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>cheltenham</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>48</v>
+      </c>
+      <c r="F44" t="n">
+        <v>484</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.578368999421631</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.2342394447657606</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.1873915558126084</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.06728395061728398</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="n">
+        <v>1.22356495468278</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>leeds</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>middlesbrough</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>48</v>
+      </c>
+      <c r="F45" t="n">
+        <v>484</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.5652658981033842</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.2359985124581629</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.1987355894384529</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.05932871099905457</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.6129755839770641</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.2685892426580719</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.1184351733648639</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.04770968587367985</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.04770968587367985</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.6129755839770641</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>42.90829087839449</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>42.90829087839449</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/predicciones.xlsx
+++ b/p6_deployment/data/england/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,28 +629,28 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.587546288237472</v>
+        <v>0.5849579090440724</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2880536949448699</v>
+        <v>0.2888652916672577</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1244000168176581</v>
+        <v>0.12617679928867</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.03420941777115782</v>
+        <v>-0.03679779696455743</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.03420941777115782</v>
+        <v>-0.03679779696455743</v>
       </c>
       <c r="X2" t="n">
-        <v>0.587546288237472</v>
+        <v>0.5849579090440724</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>41.12824017662304</v>
+        <v>1.355046592795273</v>
       </c>
       <c r="AB2" t="n">
-        <v>41.12824017662304</v>
+        <v>1.355046592795273</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2033009276898471</v>
+        <v>0.2070538117009951</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3060257948368023</v>
+        <v>0.2982431161227269</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4906732774733504</v>
+        <v>0.4947030721762778</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1974001170220624</v>
+        <v>-0.193370322319135</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1974001170220624</v>
+        <v>-0.193370322319135</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4906732774733504</v>
+        <v>0.4947030721762778</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>34.34712942313453</v>
+        <v>1.145972559792013</v>
       </c>
       <c r="AB3" t="n">
-        <v>34.34712942313453</v>
+        <v>1.145972559792013</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4449947492484919</v>
+        <v>0.4448035249157315</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3116895454487841</v>
+        <v>0.3112396944880194</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2433157053027239</v>
+        <v>0.2439567805962493</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3334172901910514</v>
+        <v>-0.3336085145238118</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3334172901910514</v>
+        <v>-0.3336085145238118</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4449947492484919</v>
+        <v>0.4448035249157315</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>31.14963244739443</v>
+        <v>1.030380975419853</v>
       </c>
       <c r="AB4" t="n">
-        <v>31.14963244739443</v>
+        <v>1.030380975419853</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2321192511673387</v>
+        <v>0.2345030970113675</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3650135583525272</v>
+        <v>0.3708512046874048</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4028671904801341</v>
+        <v>0.3946456983012278</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07620586141688346</v>
+        <v>0.06798436923797713</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07620586141688346</v>
+        <v>0.06798436923797713</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4028671904801341</v>
+        <v>0.3946456983012278</v>
       </c>
       <c r="Y5" t="n">
         <v>2.9</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>28.20070333360939</v>
+        <v>0.9141910906346924</v>
       </c>
       <c r="AB5" t="n">
-        <v>28.20070333360939</v>
+        <v>0.9141910906346924</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4646862712823306</v>
+        <v>0.4536460918938081</v>
       </c>
       <c r="R6" t="n">
-        <v>0.35636760501756</v>
+        <v>0.3681101164450714</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1789461237001093</v>
+        <v>0.1782437916611202</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2336377510640379</v>
+        <v>-0.2446779304525605</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2336377510640379</v>
+        <v>-0.2446779304525605</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4646862712823306</v>
+        <v>0.4536460918938081</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>32.52803898976315</v>
+        <v>1.05086465479225</v>
       </c>
       <c r="AB6" t="n">
-        <v>32.52803898976315</v>
+        <v>1.05086465479225</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3104057318093947</v>
+        <v>0.292385195793922</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3805739284238408</v>
+        <v>0.3734771210873065</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3090203397667642</v>
+        <v>0.3341376831187713</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1080086077587577</v>
+        <v>0.1009118004222234</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1080086077587577</v>
+        <v>0.1009118004222234</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3805739284238408</v>
+        <v>0.3734771210873065</v>
       </c>
       <c r="Y7" t="n">
         <v>3.5</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>26.64017498966886</v>
+        <v>0.865154385626424</v>
       </c>
       <c r="AB7" t="n">
-        <v>26.64017498966886</v>
+        <v>0.865154385626424</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3535423482744904</v>
+        <v>0.3671377688678597</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3934948385053813</v>
+        <v>0.3940222396115375</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2529628132201283</v>
+        <v>0.2388399915206026</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1226615051720479</v>
+        <v>0.1231889062782042</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1226615051720479</v>
+        <v>0.1231889062782042</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3934948385053813</v>
+        <v>0.3940222396115375</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>27.54463869537669</v>
+        <v>0.9127468575366325</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.54463869537669</v>
+        <v>0.9127468575366325</v>
       </c>
     </row>
     <row r="9">
@@ -1315,28 +1315,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3054699661287714</v>
+        <v>0.3072590400692738</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3865281173371165</v>
+        <v>0.3846504680684688</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3080019165341121</v>
+        <v>0.3080904918622573</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1089077207365499</v>
+        <v>0.1070300714679022</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1089077207365499</v>
+        <v>0.1070300714679022</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3865281173371165</v>
+        <v>0.3846504680684688</v>
       </c>
       <c r="Y9" t="n">
         <v>3.4</v>
@@ -1347,24 +1347,24 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>27.05696821359815</v>
+        <v>0.8910372833919838</v>
       </c>
       <c r="AB9" t="n">
-        <v>27.05696821359815</v>
+        <v>0.8910372833919838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45522.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manchester utd</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1376,7 +1376,7 @@
         <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1385,59 +1385,59 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>fa community shield</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1627462751732795</v>
+        <v>0.2296155835200828</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1782459204278775</v>
+        <v>0.2615066367867609</v>
       </c>
       <c r="N10" t="n">
-        <v>0.659007804398843</v>
+        <v>0.5088777796931563</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06861458606712745</v>
+        <v>0.06222075734270849</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3092592671082137</v>
+        <v>0.2691375851584574</v>
       </c>
       <c r="R10" t="n">
-        <v>0.335971774796851</v>
+        <v>0.3482129837401998</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3547689580949353</v>
+        <v>0.3826494311013426</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3042388463039077</v>
+        <v>-0.1262283485918137</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3042388463039077</v>
+        <v>-0.1262283485918137</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3547689580949353</v>
+        <v>0.3826494311013426</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1445,36 +1445,36 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>24.83382706664547</v>
+        <v>0.8864019100045329</v>
       </c>
       <c r="AB10" t="n">
-        <v>24.83382706664547</v>
+        <v>0.8864019100045329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45523.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>leicester</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stoke</t>
+          <t>tottenham</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1483,78 +1483,96 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
         <v>1.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1877107530910453</v>
+        <v>0.1895352559438931</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2502810041213938</v>
+        <v>0.2429939178767861</v>
       </c>
       <c r="N11" t="n">
-        <v>0.562008242787561</v>
+        <v>0.5674708261793209</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06546906187624746</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+        <v>0.05521265161983724</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1587052991781667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.295277000122409</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.5460177006994242</v>
+      </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>-0.02145312547989664</v>
+      </c>
       <c r="V11" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.02145312547989664</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.5460177006994242</v>
+      </c>
       <c r="Y11" t="n">
-        <v>1.251874062968516</v>
+        <v>1.67</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.264842159579928</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.264842159579928</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45514.45833333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>leyton orient</t>
+          <t>manchester utd</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>newport</t>
+          <t>manchester city</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1563,56 +1581,76 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>fa community shield</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.53</v>
+        <v>5.25</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>1.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6106870229007634</v>
+        <v>0.1779141104294479</v>
       </c>
       <c r="M12" t="n">
-        <v>0.233587786259542</v>
+        <v>0.1779141104294479</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1557251908396947</v>
+        <v>0.6441717791411044</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0702614379084967</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+        <v>0.07060755336617408</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.323451801032713</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3350808055759071</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3414673933913798</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.3027043857497245</v>
+      </c>
       <c r="V12" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.3027043857497245</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.3414673933913798</v>
+      </c>
       <c r="Y12" t="n">
-        <v>1.219123505976096</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.7910043112705579</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7910043112705579</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1620,12 +1658,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>stockport county</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>blackburn</t>
+          <t>stoke</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1645,25 +1683,25 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3479328694228407</v>
+        <v>0.1778625292537055</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2762996316004912</v>
+        <v>0.2457311259426194</v>
       </c>
       <c r="N13" t="n">
-        <v>0.375767498976668</v>
+        <v>0.5764063448036751</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06448801742919397</v>
+        <v>0.07091803583031653</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1679,7 +1717,7 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>1.298076923076923</v>
+        <v>1.237991266375546</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1692,20 +1730,20 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>barrow</t>
+          <t>leyton orient</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>port vale</t>
+          <t>newport</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1725,25 +1763,25 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>6.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3765084473049075</v>
+        <v>0.6191950464396284</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2614641995172969</v>
+        <v>0.2321981424148607</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3620273531777956</v>
+        <v>0.1486068111455108</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06239316239316239</v>
+        <v>0.07666666666666666</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1757,7 +1795,7 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>1.274509803921569</v>
+        <v>1.209677419354839</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -1770,20 +1808,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bolton</t>
+          <t>stockport county</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>mansfield</t>
+          <t>blackburn</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1803,31 +1841,33 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5653773669568339</v>
+        <v>0.3479328694228407</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2248048101947411</v>
+        <v>0.2762996316004912</v>
       </c>
       <c r="N15" t="n">
-        <v>0.209817822848425</v>
+        <v>0.375767498976668</v>
       </c>
       <c r="O15" t="n">
-        <v>0.05911985552704113</v>
+        <v>0.06448801742919397</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
         <v>-100</v>
@@ -1835,7 +1875,7 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>1.217990275526742</v>
+        <v>1.298076923076923</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -1848,7 +1888,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1856,12 +1896,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bristol city</t>
+          <t>barrow</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>coventry</t>
+          <t>port vale</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1881,72 +1921,52 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3620273531777956</v>
+        <v>0.3765084473049075</v>
       </c>
       <c r="M16" t="n">
         <v>0.2614641995172969</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3765084473049075</v>
+        <v>0.3620273531777956</v>
       </c>
       <c r="O16" t="n">
         <v>0.06239316239316239</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.4879081638868339</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.273786198928091</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.238305637185075</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.1258808107090383</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.1258808107090383</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.4879081638868339</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>2.6</v>
+        <v>1.274509803921569</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>34.15357147207837</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>34.15357147207837</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1954,12 +1974,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bromley</t>
+          <t>bolton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>afc wimbledon</t>
+          <t>mansfield</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1979,25 +1999,25 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3231597845601437</v>
+        <v>0.5683355886332883</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2603231597845602</v>
+        <v>0.2232746955345061</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4165170556552962</v>
+        <v>0.2083897158322057</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06704980842911867</v>
+        <v>0.06637806637806642</v>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -2011,7 +2031,7 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>1.266990291262136</v>
+        <v>1.207317073170732</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2024,7 +2044,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2032,12 +2052,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>burton</t>
+          <t>bristol city</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>blackpool</t>
+          <t>coventry</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2057,52 +2077,72 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3234659870613605</v>
+        <v>0.3692307692307692</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2501470299941188</v>
+        <v>0.2615384615384615</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4263869829445207</v>
+        <v>0.3692307692307692</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06603970741901777</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+        <v>0.06209150326797408</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4819338886054317</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.274275824353968</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2437902870406003</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1127031193746625</v>
+      </c>
       <c r="V18" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1127031193746625</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.4819338886054317</v>
+      </c>
       <c r="Y18" t="n">
-        <v>1.250980392156863</v>
+        <v>2.55</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.116392929492239</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.116392929492239</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2110,12 +2150,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cambridge utd</t>
+          <t>bromley</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>qpr</t>
+          <t>afc wimbledon</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2135,33 +2175,31 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="L19" t="n">
-        <v>0.216998191681736</v>
+        <v>0.3231597845601437</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2610006027727547</v>
+        <v>0.2603231597845602</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5220012055455093</v>
+        <v>0.4165170556552962</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06704980842911867</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
         <v>-100</v>
@@ -2169,7 +2207,7 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>1.271451876019576</v>
+        <v>1.266990291262136</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2182,7 +2220,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2190,12 +2228,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cardiff</t>
+          <t>burton</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>bristol rovers</t>
+          <t>blackpool</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2215,33 +2253,31 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5791912384161751</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2502106149957877</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1705981465880371</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06576879910213251</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
         <v>-100</v>
@@ -2249,7 +2285,7 @@
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>1.251404494382022</v>
+        <v>1.252427184466019</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2262,7 +2298,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2270,12 +2306,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>charlton</t>
+          <t>cambridge utd</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>birmingham</t>
+          <t>qpr</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2295,25 +2331,25 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3039936419630439</v>
+        <v>0.2088709677419355</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2771706735545401</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="N21" t="n">
-        <v>0.418835684482416</v>
+        <v>0.5370967741935484</v>
       </c>
       <c r="O21" t="n">
-        <v>0.06114273666455827</v>
+        <v>0.06392106392106389</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -2329,7 +2365,7 @@
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="n">
-        <v>1.303738317757009</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2342,7 +2378,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -2350,12 +2386,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>colchester</t>
+          <t>cardiff</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>bristol rovers</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2375,31 +2411,33 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.33</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8</v>
+        <v>5.75</v>
       </c>
       <c r="L22" t="n">
-        <v>0.216998191681736</v>
+        <v>0.5884729329383249</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2610006027727547</v>
+        <v>0.2477780770266631</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5220012055455093</v>
+        <v>0.1637489900350121</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06207093821510279</v>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
         <v>-100</v>
@@ -2407,7 +2445,7 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>1.271451876019576</v>
+        <v>1.251700680272109</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2420,7 +2458,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -2428,12 +2466,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>crawley</t>
+          <t>charlton</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>swindon</t>
+          <t>birmingham</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2453,31 +2491,33 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
         <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.3039936419630439</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2771706735545401</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.418835684482416</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.06114273666455827</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
         <v>-100</v>
@@ -2485,7 +2525,7 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
-        <v>1.298181818181818</v>
+        <v>1.303738317757009</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2498,7 +2538,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -2506,12 +2546,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>derby</t>
+          <t>colchester</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>chesterfield</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2531,25 +2571,25 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.57</v>
+        <v>4.33</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5977796754910334</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2681468830059778</v>
+        <v>0.2610006027727547</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1340734415029889</v>
+        <v>0.5220012055455093</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06551410373066413</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -2563,7 +2603,7 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>1.282380396732789</v>
+        <v>1.271451876019576</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2576,7 +2616,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -2584,12 +2624,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fleetwood</t>
+          <t>crawley</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>west brom</t>
+          <t>swindon</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2609,33 +2649,31 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1705981465880371</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2502106149957877</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5791912384161753</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06576879910213229</v>
+        <v>0.06442577030812324</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
         <v>-100</v>
@@ -2643,7 +2681,7 @@
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>1.251404494382022</v>
+        <v>1.298181818181818</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -2656,7 +2694,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2664,12 +2702,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>grimsby</t>
+          <t>derby</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>bradford city</t>
+          <t>chesterfield</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2689,25 +2727,25 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.6127132076364411</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.2533651912658796</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.1339216010976793</v>
       </c>
       <c r="O26" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.06672218436924315</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2721,7 +2759,7 @@
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.25556858147714</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2734,7 +2772,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2742,12 +2780,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>huddersfield</t>
+          <t>fleetwood</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>morecambe</t>
+          <t>west brom</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2767,25 +2805,25 @@
         </is>
       </c>
       <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K27" t="n">
         <v>1.57</v>
       </c>
-      <c r="J27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.595120015869867</v>
+        <v>0.1562352694704865</v>
       </c>
       <c r="M27" t="n">
-        <v>0.249156913310851</v>
+        <v>0.2466872675849787</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1557230708192819</v>
+        <v>0.5970774629445346</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0702760084925691</v>
+        <v>0.06676723656274453</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2814,7 +2852,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2822,12 +2860,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lincoln</t>
+          <t>grimsby</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>harrogate</t>
+          <t>bradford city</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2847,25 +2885,25 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>6.5</v>
+        <v>2.63</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6297577854671281</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2249134948096886</v>
+        <v>0.2777416734362307</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1453287197231834</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0586080586080584</v>
+        <v>0.05896116855633737</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -2879,7 +2917,7 @@
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>1.21875</v>
+        <v>1.307456978967495</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -2892,7 +2930,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2900,12 +2938,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>northampton</t>
+          <t>huddersfield</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>wycombe</t>
+          <t>morecambe</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2925,31 +2963,33 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3958218801539307</v>
+        <v>0.5970774629445346</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2770753161077515</v>
+        <v>0.2466872675849787</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3271028037383177</v>
+        <v>0.1562352694704865</v>
       </c>
       <c r="O29" t="n">
-        <v>0.06150793650793651</v>
+        <v>0.06676723656274453</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
         <v>-100</v>
@@ -2957,7 +2997,7 @@
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>1.303117870722433</v>
+        <v>1.244385733157199</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -2970,7 +3010,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -2978,12 +3018,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>norwich</t>
+          <t>lincoln</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>stevenage</t>
+          <t>harrogate</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3003,33 +3043,31 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="J30" t="n">
         <v>4.33</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6264014466546112</v>
+        <v>0.6485017704889973</v>
       </c>
       <c r="M30" t="n">
-        <v>0.216998191681736</v>
+        <v>0.2171657199097104</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1566003616636528</v>
+        <v>0.1343325096012923</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06345919748802609</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
         <v>-100</v>
@@ -3037,7 +3075,7 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.201183431952663</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3050,7 +3088,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -3058,12 +3096,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>oxford utd</t>
+          <t>northampton</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>peterborough</t>
+          <t>wycombe</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3083,25 +3121,25 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4165170556552962</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2603231597845602</v>
+        <v>0.2768860353130017</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3231597845601437</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="O31" t="n">
-        <v>0.06704980842911867</v>
+        <v>0.06223358908780896</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -3115,7 +3153,7 @@
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>1.266990291262136</v>
+        <v>1.30188679245283</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3128,7 +3166,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -3136,12 +3174,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>portsmouth</t>
+          <t>norwich</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>millwall</t>
+          <t>stevenage</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3161,25 +3199,25 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="K32" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3774574049803408</v>
+        <v>0.6500776404176282</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2948885976408912</v>
+        <v>0.2161921021250311</v>
       </c>
       <c r="N32" t="n">
-        <v>0.327653997378768</v>
+        <v>0.1337302574573407</v>
       </c>
       <c r="O32" t="n">
-        <v>0.05972222222222223</v>
+        <v>0.06824846951867736</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -3195,7 +3233,7 @@
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="n">
-        <v>1.338289962825279</v>
+        <v>1.194312796208531</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3208,7 +3246,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -3216,12 +3254,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>preston</t>
+          <t>oxford utd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>sunderland</t>
+          <t>peterborough</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3241,72 +3279,52 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K33" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3958218801539307</v>
+        <v>0.4265402843601896</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2770753161077515</v>
+        <v>0.2606635071090048</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3271028037383177</v>
+        <v>0.3127962085308057</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06150793650793651</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.3904461185194874</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.3346801439734999</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.2748737375070125</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>-0.005375761634443366</v>
-      </c>
+        <v>0.06565656565656552</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>-0.005375761634443366</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.3904461185194874</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="n">
-        <v>2.38</v>
+        <v>1.269230769230769</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA33" t="n">
-        <v>27.33122829636411</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>27.33122829636411</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -3314,12 +3332,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rotherham</t>
+          <t>portsmouth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>crewe</t>
+          <t>millwall</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3339,25 +3357,25 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="J34" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5816922989614663</v>
+        <v>0.3830753353973168</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2298393961750184</v>
+        <v>0.2932920536635707</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1884683048635151</v>
+        <v>0.3236326109391125</v>
       </c>
       <c r="O34" t="n">
-        <v>0.06118638964167422</v>
+        <v>0.06549085151301903</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -3373,7 +3391,7 @@
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>1.22356495468278</v>
+        <v>1.32803738317757</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -3386,7 +3404,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -3394,12 +3412,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>salford</t>
+          <t>preston</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>doncaster</t>
+          <t>sunderland</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3422,49 +3440,69 @@
         <v>2.3</v>
       </c>
       <c r="J35" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K35" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2621082621082621</v>
+        <v>0.2768860353130017</v>
       </c>
       <c r="N35" t="n">
-        <v>0.3276353276353276</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05978260869565233</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+        <v>0.06223358908780896</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.3879807965669084</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.3318384937874302</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2801807096456617</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.02132899476535488</v>
+      </c>
       <c r="V35" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-0.02132899476535488</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.3879807965669084</v>
+      </c>
       <c r="Y35" t="n">
-        <v>1.278764478764479</v>
+        <v>2.3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.8987519415151199</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.8987519415151199</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3472,12 +3510,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>shrewsbury</t>
+          <t>rotherham</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>notts co</t>
+          <t>crewe</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3497,31 +3535,33 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="J36" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4093097913322633</v>
+        <v>0.5977796754910334</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2768860353130017</v>
+        <v>0.2234557358383149</v>
       </c>
       <c r="N36" t="n">
-        <v>0.3138041733547351</v>
+        <v>0.1787645886706519</v>
       </c>
       <c r="O36" t="n">
-        <v>0.06223358908780896</v>
+        <v>0.06551410373066413</v>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
         <v>-100</v>
@@ -3529,7 +3569,7 @@
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>1.30188679245283</v>
+        <v>1.208577712609971</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3542,7 +3582,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -3550,12 +3590,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>swansea</t>
+          <t>salford</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>gillingham</t>
+          <t>doncaster</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3575,33 +3615,31 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="J37" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6264014466546112</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="M37" t="n">
-        <v>0.216998191681736</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1566003616636528</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="O37" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
         <v>-100</v>
@@ -3609,7 +3647,7 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3622,7 +3660,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -3630,12 +3668,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tranmere</t>
+          <t>shrewsbury</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>accrington</t>
+          <t>notts co</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3655,25 +3693,25 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="J38" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4485336400230017</v>
+        <v>0.418835684482416</v>
       </c>
       <c r="M38" t="n">
-        <v>0.261644623346751</v>
+        <v>0.2771706735545401</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2898217366302473</v>
+        <v>0.3039936419630439</v>
       </c>
       <c r="O38" t="n">
-        <v>0.06166056166056166</v>
+        <v>0.06114273666455827</v>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -3687,7 +3725,7 @@
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
-        <v>1.275700934579439</v>
+        <v>1.303738317757009</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -3700,7 +3738,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -3708,12 +3746,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>walsall</t>
+          <t>swansea</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>exeter</t>
+          <t>gillingham</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3733,31 +3771,33 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="J39" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.6500776404176282</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2161921021250311</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.1337302574573407</v>
       </c>
       <c r="O39" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.06824846951867736</v>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
         <v>-100</v>
@@ -3765,7 +3805,7 @@
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>1.272727272727273</v>
+        <v>1.194312796208531</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -3778,7 +3818,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -3786,12 +3826,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>watford</t>
+          <t>tranmere</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>mk dons</t>
+          <t>accrington</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3811,33 +3851,31 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="J40" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6264014466546112</v>
+        <v>0.4564841498559078</v>
       </c>
       <c r="M40" t="n">
-        <v>0.216998191681736</v>
+        <v>0.2599423631123919</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1566003616636528</v>
+        <v>0.2835734870317003</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06861295885686136</v>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
         <v>-100</v>
@@ -3845,7 +3883,7 @@
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>1.264485981308411</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -3858,7 +3896,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -3866,12 +3904,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wigan</t>
+          <t>walsall</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>barnsley</t>
+          <t>exeter</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3891,25 +3929,25 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K41" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.418835684482416</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2771706735545401</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N41" t="n">
-        <v>0.3039936419630439</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="O41" t="n">
-        <v>0.06114273666455827</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -3923,7 +3961,7 @@
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="n">
-        <v>1.303738317757009</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -3936,20 +3974,20 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45517.66666666666</v>
+        <v>45517.65625</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sheffield utd</t>
+          <t>watford</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>wrexham</t>
+          <t>mk dons</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3969,25 +4007,25 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="K42" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5993833395353783</v>
+        <v>0.6264014466546112</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2295199617245229</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1710966987400989</v>
+        <v>0.1566003616636528</v>
       </c>
       <c r="O42" t="n">
-        <v>0.06266329600180764</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -4003,7 +4041,7 @@
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="n">
-        <v>1.221357850070721</v>
+        <v>1.2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -4016,20 +4054,20 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hull</t>
+          <t>wigan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>sheffield wed</t>
+          <t>barnsley</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4049,85 +4087,65 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="J43" t="n">
         <v>3.4</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4903728275762602</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2754741472560756</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="N43" t="n">
-        <v>0.2341530251676643</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="O43" t="n">
-        <v>0.06767785648290725</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.4576062362731794</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.3133115276720925</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.2290822360547282</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>-0.03276659130308085</v>
-      </c>
+        <v>0.05106209150326801</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
-        <v>1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>-0.03276659130308085</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.4576062362731794</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>1.91</v>
+        <v>1.321100917431193</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA43" t="n">
-        <v>32.03243653912256</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>32.03243653912256</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>plymouth</t>
+          <t>sheffield utd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cheltenham</t>
+          <t>wrexham</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4147,25 +4165,25 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K44" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="L44" t="n">
-        <v>0.578368999421631</v>
+        <v>0.6133566993028307</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2342394447657606</v>
+        <v>0.2234370833174597</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1873915558126084</v>
+        <v>0.1632062173797097</v>
       </c>
       <c r="O44" t="n">
-        <v>0.06728395061728398</v>
+        <v>0.06560305281532886</v>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -4181,7 +4199,7 @@
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
-        <v>1.22356495468278</v>
+        <v>1.208447802197802</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4194,20 +4212,20 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>697ha3El</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45518.66666666666</v>
+        <v>45518.65625</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>leeds</t>
+          <t>hull</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>middlesbrough</t>
+          <t>sheffield wed</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4227,66 +4245,244 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="J45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K45" t="n">
         <v>4</v>
       </c>
-      <c r="K45" t="n">
-        <v>4.75</v>
-      </c>
       <c r="L45" t="n">
-        <v>0.5652658981033842</v>
+        <v>0.4903728275762602</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2359985124581629</v>
+        <v>0.2754741472560756</v>
       </c>
       <c r="N45" t="n">
-        <v>0.1987355894384529</v>
+        <v>0.2341530251676643</v>
       </c>
       <c r="O45" t="n">
-        <v>0.05932871099905457</v>
+        <v>0.06767785648290725</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.6129755839770641</v>
+        <v>0.4598349839791374</v>
       </c>
       <c r="R45" t="n">
-        <v>0.2685892426580719</v>
+        <v>0.3143145489397912</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1184351733648639</v>
+        <v>0.2258504670810714</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04770968587367985</v>
+        <v>-0.03053784359712286</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>0.04770968587367985</v>
+        <v>-0.03053784359712286</v>
       </c>
       <c r="X45" t="n">
-        <v>0.6129755839770641</v>
+        <v>0.4598349839791374</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.065201134398292</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.065201134398292</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>plymouth</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>cheltenham</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>48</v>
+      </c>
+      <c r="F46" t="n">
+        <v>484</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.5945393528428787</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.2276650692593463</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.1777955778977751</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.07132130465981623</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="n">
+        <v>1.208577712609971</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>leeds</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>middlesbrough</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>48</v>
+      </c>
+      <c r="F47" t="n">
+        <v>484</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="J47" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.5652658981033842</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.2359985124581629</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.1987355894384529</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.05932871099905457</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.6034479663954815</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.2693771610451108</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.1271748725594075</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.03818206829209725</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.03818206829209725</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.6034479663954815</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z47" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA45" t="n">
-        <v>42.90829087839449</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>42.90829087839449</v>
+      <c r="AA47" t="n">
+        <v>1.397878545021648</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.397878545021648</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/predicciones.xlsx
+++ b/p6_deployment/data/england/predicciones.xlsx
@@ -629,28 +629,28 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5849579090440724</v>
+        <v>0.5478121359331051</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2888652916672577</v>
+        <v>0.3193946784018565</v>
       </c>
       <c r="S2" t="n">
-        <v>0.12617679928867</v>
+        <v>0.1327931856650388</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.03679779696455743</v>
+        <v>-0.07394357007552477</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.03679779696455743</v>
+        <v>-0.07394357007552477</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5849579090440724</v>
+        <v>0.5478121359331051</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>1.355046592795273</v>
+        <v>3.889293414211416</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.355046592795273</v>
+        <v>3.889293414211416</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2070538117009951</v>
+        <v>0.2075059145687156</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2982431161227269</v>
+        <v>0.2996237109575965</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4947030721762778</v>
+        <v>0.4928703744736879</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.193370322319135</v>
+        <v>-0.1952030200217249</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.193370322319135</v>
+        <v>-0.1952030200217249</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4947030721762778</v>
+        <v>0.4928703744736879</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>1.145972559792013</v>
+        <v>3.499224233569205</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.145972559792013</v>
+        <v>3.499224233569205</v>
       </c>
     </row>
     <row r="4">
@@ -804,49 +804,49 @@
         <v>1.22</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="K4" t="n">
         <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7784120394395433</v>
+        <v>0.7833716315019844</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1582771146860404</v>
+        <v>0.1529141424691874</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06331084587441618</v>
+        <v>0.06371422602882806</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0530054644808744</v>
+        <v>0.0463387978142078</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4448035249157315</v>
+        <v>0.4467977924840937</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3112396944880194</v>
+        <v>0.3094895004568461</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2439567805962493</v>
+        <v>0.2437127070590602</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3336085145238118</v>
+        <v>-0.3365738390178907</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3336085145238118</v>
+        <v>-0.3365738390178907</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4448035249157315</v>
+        <v>0.4467977924840937</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>1.030380975419853</v>
+        <v>3.172123430293599</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.030380975419853</v>
+        <v>3.172123430293599</v>
       </c>
     </row>
     <row r="5">
@@ -899,55 +899,55 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3947157726180945</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2786228983186549</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3266613290632506</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05561189993238669</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2345030970113675</v>
+        <v>0.2278268765141783</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3708512046874048</v>
+        <v>0.3619384246905776</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3946456983012278</v>
+        <v>0.4102346987952438</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06798436923797713</v>
+        <v>0.07939031083750286</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06798436923797713</v>
+        <v>0.07939031083750286</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3946456983012278</v>
+        <v>0.4102346987952438</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>0.9141910906346924</v>
+        <v>2.91253699516467</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9141910906346924</v>
+        <v>2.91253699516467</v>
       </c>
     </row>
     <row r="6">
@@ -997,55 +997,55 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="K6" t="n">
         <v>8.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6983240223463686</v>
+        <v>0.7093184979137691</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1899441340782123</v>
+        <v>0.1796940194714882</v>
       </c>
       <c r="N6" t="n">
-        <v>0.111731843575419</v>
+        <v>0.1109874826147427</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05294117647058827</v>
+        <v>0.06000294854784016</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4536460918938081</v>
+        <v>0.4854916296044625</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3681101164450714</v>
+        <v>0.3445222740792314</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1782437916611202</v>
+        <v>0.1699860963163061</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2446779304525605</v>
+        <v>-0.2238268683093066</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2446779304525605</v>
+        <v>-0.2238268683093066</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4536460918938081</v>
+        <v>0.4854916296044625</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>1.05086465479225</v>
+        <v>3.446837471862763</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.05086465479225</v>
+        <v>3.446837471862763</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.292385195793922</v>
+        <v>0.3022649971005809</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3734771210873065</v>
+        <v>0.3669991019301996</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3341376831187713</v>
+        <v>0.3307359009692193</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1009118004222234</v>
+        <v>0.09443378126511648</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1009118004222234</v>
+        <v>0.09443378126511648</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3734771210873065</v>
+        <v>0.3669991019301996</v>
       </c>
       <c r="Y7" t="n">
         <v>3.5</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>0.865154385626424</v>
+        <v>2.605577891638621</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.865154385626424</v>
+        <v>2.605577891638621</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3671377688678597</v>
+        <v>0.3805482879075007</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3940222396115375</v>
+        <v>0.396365754989814</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2388399915206026</v>
+        <v>0.2230859571026854</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1231889062782042</v>
+        <v>0.1255324216564806</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1231889062782042</v>
+        <v>0.1255324216564806</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3940222396115375</v>
+        <v>0.396365754989814</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>0.9127468575366325</v>
+        <v>2.81407186767594</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9127468575366325</v>
+        <v>2.81407186767594</v>
       </c>
     </row>
     <row r="9">
@@ -1315,28 +1315,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3072590400692738</v>
+        <v>0.3106801764048837</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3846504680684688</v>
+        <v>0.384110555074948</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3080904918622573</v>
+        <v>0.3052092685201684</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1070300714679022</v>
+        <v>0.1064901584743814</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1070300714679022</v>
+        <v>0.1064901584743814</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3846504680684688</v>
+        <v>0.384110555074948</v>
       </c>
       <c r="Y9" t="n">
         <v>3.4</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>0.8910372833919838</v>
+        <v>2.72706381292092</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8910372833919838</v>
+        <v>2.72706381292092</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2691375851584574</v>
+        <v>0.2820386913923193</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3482129837401998</v>
+        <v>0.3396646854508487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3826494311013426</v>
+        <v>0.3782966231568318</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1262283485918137</v>
+        <v>-0.1305811565363245</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1262283485918137</v>
+        <v>-0.1305811565363245</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3826494311013426</v>
+        <v>0.3782966231568318</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>0.8864019100045329</v>
+        <v>2.685786729708283</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8864019100045329</v>
+        <v>2.685786729708283</v>
       </c>
     </row>
     <row r="11">
@@ -1511,28 +1511,28 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1587052991781667</v>
+        <v>0.1725710825428429</v>
       </c>
       <c r="R11" t="n">
-        <v>0.295277000122409</v>
+        <v>0.3082493863644105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5460177006994242</v>
+        <v>0.5191795310927471</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.02145312547989664</v>
+        <v>-0.04829129508657382</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.02145312547989664</v>
+        <v>-0.04829129508657382</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5460177006994242</v>
+        <v>0.5191795310927471</v>
       </c>
       <c r="Y11" t="n">
         <v>1.67</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>1.264842159579928</v>
+        <v>3.686010949050913</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.264842159579928</v>
+        <v>3.686010949050913</v>
       </c>
     </row>
     <row r="12">
@@ -1585,55 +1585,55 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="K12" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1779141104294479</v>
+        <v>0.2061603080154008</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1779141104294479</v>
+        <v>0.1953097654882744</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6441717791411044</v>
+        <v>0.5985299264963249</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07060755336617408</v>
+        <v>0.07790982833427651</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.323451801032713</v>
+        <v>0.3028390567587279</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3350808055759071</v>
+        <v>0.3365992230389832</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3414673933913798</v>
+        <v>0.3605617202022888</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3027043857497245</v>
+        <v>-0.2379682062940361</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3027043857497245</v>
+        <v>-0.2379682062940361</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3414673933913798</v>
+        <v>0.3605617202022888</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>0.7910043112705579</v>
+        <v>2.55987451137947</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.7910043112705579</v>
+        <v>2.55987451137947</v>
       </c>
     </row>
     <row r="13">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
         <v>3.8</v>
@@ -1692,16 +1692,16 @@
         <v>1.62</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1778625292537055</v>
+        <v>0.171161652671968</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2457311259426194</v>
+        <v>0.2477339709725852</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5764063448036751</v>
+        <v>0.5811043763554469</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07091803583031653</v>
+        <v>0.06226002717230772</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>1.237991266375546</v>
+        <v>1.251404494382022</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1766,22 +1766,22 @@
         <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6191950464396284</v>
+        <v>0.6263219741480611</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2321981424148607</v>
+        <v>0.2291421856639248</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1486068111455108</v>
+        <v>0.1445358401880141</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07666666666666666</v>
+        <v>0.06441525953721072</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1795,7 +1795,7 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>1.209677419354839</v>
+        <v>1.21875</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2101,28 +2101,28 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4819338886054317</v>
+        <v>0.4837268191341964</v>
       </c>
       <c r="R18" t="n">
-        <v>0.274275824353968</v>
+        <v>0.2733478735333315</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2437902870406003</v>
+        <v>0.2429253073324721</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1127031193746625</v>
+        <v>0.1144960499034272</v>
       </c>
       <c r="V18" t="n">
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1127031193746625</v>
+        <v>0.1144960499034272</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4819338886054317</v>
+        <v>0.4837268191341964</v>
       </c>
       <c r="Y18" t="n">
         <v>2.55</v>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>1.116392929492239</v>
+        <v>3.434307874051561</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.116392929492239</v>
+        <v>3.434307874051561</v>
       </c>
     </row>
     <row r="19">
@@ -2727,25 +2727,25 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6127132076364411</v>
+        <v>0.5991550377672512</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2533651912658796</v>
+        <v>0.2579695301497887</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1339216010976793</v>
+        <v>0.1428754320829599</v>
       </c>
       <c r="O26" t="n">
-        <v>0.06672218436924315</v>
+        <v>0.07678522194651238</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>1.25556858147714</v>
+        <v>1.251552795031056</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3461,28 +3461,28 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3879807965669084</v>
+        <v>0.3897291218114294</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3318384937874302</v>
+        <v>0.3323829537189195</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2801807096456617</v>
+        <v>0.2778879244696511</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.02132899476535488</v>
+        <v>-0.01958066952083393</v>
       </c>
       <c r="V35" t="n">
         <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.02132899476535488</v>
+        <v>-0.01958066952083393</v>
       </c>
       <c r="X35" t="n">
-        <v>0.3879807965669084</v>
+        <v>0.3897291218114294</v>
       </c>
       <c r="Y35" t="n">
         <v>2.3</v>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>0.8987519415151199</v>
+        <v>2.766953864951772</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.8987519415151199</v>
+        <v>2.766953864951772</v>
       </c>
     </row>
     <row r="36">
@@ -4269,28 +4269,28 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.4598349839791374</v>
+        <v>0.4583953404723956</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3143145489397912</v>
+        <v>0.3140287278096991</v>
       </c>
       <c r="S45" t="n">
-        <v>0.2258504670810714</v>
+        <v>0.2275759317179051</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>-0.03053784359712286</v>
+        <v>-0.03197748710386461</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>-0.03053784359712286</v>
+        <v>-0.03197748710386461</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4598349839791374</v>
+        <v>0.4583953404723956</v>
       </c>
       <c r="Y45" t="n">
         <v>1.91</v>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>1.065201134398292</v>
+        <v>3.254462363758577</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.065201134398292</v>
+        <v>3.254462363758577</v>
       </c>
     </row>
     <row r="46">
@@ -4349,19 +4349,19 @@
         <v>4.1</v>
       </c>
       <c r="K46" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5945393528428787</v>
+        <v>0.5993833395353783</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2276650692593463</v>
+        <v>0.2295199617245229</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1777955778977751</v>
+        <v>0.1710966987400989</v>
       </c>
       <c r="O46" t="n">
-        <v>0.07132130465981623</v>
+        <v>0.06266329600180764</v>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -4377,7 +4377,7 @@
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
-        <v>1.208577712609971</v>
+        <v>1.221357850070721</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4447,28 +4447,28 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.6034479663954815</v>
+        <v>0.6016001238134623</v>
       </c>
       <c r="R47" t="n">
-        <v>0.2693771610451108</v>
+        <v>0.2709673188211533</v>
       </c>
       <c r="S47" t="n">
-        <v>0.1271748725594075</v>
+        <v>0.1274325573653845</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0.03818206829209725</v>
+        <v>0.03633422571007805</v>
       </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03818206829209725</v>
+        <v>0.03633422571007805</v>
       </c>
       <c r="X47" t="n">
-        <v>0.6034479663954815</v>
+        <v>0.6016001238134623</v>
       </c>
       <c r="Y47" t="n">
         <v>1.67</v>
@@ -4479,10 +4479,10 @@
         </is>
       </c>
       <c r="AA47" t="n">
-        <v>1.397878545021648</v>
+        <v>4.271171166281338</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.397878545021648</v>
+        <v>4.271171166281338</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/predicciones.xlsx
+++ b/p6_deployment/data/england/predicciones.xlsx
@@ -629,28 +629,28 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5478121359331051</v>
+        <v>0.5472927597399772</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3193946784018565</v>
+        <v>0.3174877309452435</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1327931856650388</v>
+        <v>0.1352195093147789</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07394357007552477</v>
+        <v>-0.07446294626865269</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.07394357007552477</v>
+        <v>-0.07446294626865269</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5478121359331051</v>
+        <v>0.5472927597399772</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>3.889293414211416</v>
+        <v>6.884337015187532</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.889293414211416</v>
+        <v>6.884337015187532</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2075059145687156</v>
+        <v>0.2100382114772122</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2996237109575965</v>
+        <v>0.2980519455785725</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4928703744736879</v>
+        <v>0.4919098429442151</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1952030200217249</v>
+        <v>-0.1961635515511977</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1952030200217249</v>
+        <v>-0.1961635515511977</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4928703744736879</v>
+        <v>0.4919098429442151</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>3.499224233569205</v>
+        <v>6.187681235770201</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.499224233569205</v>
+        <v>6.187681235770201</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4467977924840937</v>
+        <v>0.4465517429240594</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3094895004568461</v>
+        <v>0.3099576327625041</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2437127070590602</v>
+        <v>0.2434906243134364</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3365738390178907</v>
+        <v>-0.336819888577925</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3365738390178907</v>
+        <v>-0.336819888577925</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4467977924840937</v>
+        <v>0.4465517429240594</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>3.172123430293599</v>
+        <v>5.617126553015594</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.172123430293599</v>
+        <v>5.617126553015594</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2278268765141783</v>
+        <v>0.2312737815347075</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3619384246905776</v>
+        <v>0.364304302167788</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4102346987952438</v>
+        <v>0.4044219162975047</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07939031083750286</v>
+        <v>0.07357752833976383</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07939031083750286</v>
+        <v>0.07357752833976383</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4102346987952438</v>
+        <v>0.4044219162975047</v>
       </c>
       <c r="Y5" t="n">
         <v>2.88</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>2.91253699516467</v>
+        <v>5.087179975563296</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.91253699516467</v>
+        <v>5.087179975563296</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4854916296044625</v>
+        <v>0.4860935572145377</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3445222740792314</v>
+        <v>0.346874166327044</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1699860963163061</v>
+        <v>0.1670322764584181</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2238268683093066</v>
+        <v>-0.2232249406992314</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2238268683093066</v>
+        <v>-0.2232249406992314</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4854916296044625</v>
+        <v>0.4860935572145377</v>
       </c>
       <c r="Y6" t="n">
         <v>1.33</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>3.446837471862763</v>
+        <v>6.114518800442628</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.446837471862763</v>
+        <v>6.114518800442628</v>
       </c>
     </row>
     <row r="7">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>2.605577891638621</v>
+        <v>4.616442401246155</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.605577891638621</v>
+        <v>4.616442401246155</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3805482879075007</v>
+        <v>0.3743799427639963</v>
       </c>
       <c r="R8" t="n">
-        <v>0.396365754989814</v>
+        <v>0.3946336719648086</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2230859571026854</v>
+        <v>0.2309863852711951</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1255324216564806</v>
+        <v>0.1238003386314753</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1255324216564806</v>
+        <v>0.1238003386314753</v>
       </c>
       <c r="X8" t="n">
-        <v>0.396365754989814</v>
+        <v>0.3946336719648086</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>2.81407186767594</v>
+        <v>4.964054698325397</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.81407186767594</v>
+        <v>4.964054698325397</v>
       </c>
     </row>
     <row r="9">
@@ -1291,52 +1291,52 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.277992277992278</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.05800653594771243</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3106801764048837</v>
+        <v>0.3144227816646827</v>
       </c>
       <c r="R9" t="n">
-        <v>0.384110555074948</v>
+        <v>0.3842052001281865</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3052092685201684</v>
+        <v>0.3013720182071305</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1064901584743814</v>
+        <v>0.1062129221359085</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1064901584743814</v>
+        <v>0.1062129221359085</v>
       </c>
       <c r="X9" t="n">
-        <v>0.384110555074948</v>
+        <v>0.3842052001281865</v>
       </c>
       <c r="Y9" t="n">
         <v>3.4</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>2.72706381292092</v>
+        <v>4.832876067877577</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.72706381292092</v>
+        <v>4.832876067877577</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2820386913923193</v>
+        <v>0.2820683392247597</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3396646854508487</v>
+        <v>0.3380256032651838</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3782966231568318</v>
+        <v>0.3799060575100564</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1305811565363245</v>
+        <v>-0.1289717221830999</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1305811565363245</v>
+        <v>-0.1289717221830999</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3782966231568318</v>
+        <v>0.3799060575100564</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>2.685786729708283</v>
+        <v>4.778797613279301</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.685786729708283</v>
+        <v>4.778797613279301</v>
       </c>
     </row>
     <row r="11">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>3.686010949050913</v>
+        <v>6.53070372267968</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.686010949050913</v>
+        <v>6.53070372267968</v>
       </c>
     </row>
     <row r="12">
@@ -1591,49 +1591,49 @@
         <v>4.75</v>
       </c>
       <c r="K12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2061603080154008</v>
+        <v>0.2077442718852288</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1953097654882744</v>
+        <v>0.1968103628386378</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5985299264963249</v>
+        <v>0.5954453652761335</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07790982833427651</v>
+        <v>0.06969121317093152</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3028390567587279</v>
+        <v>0.2992414176127644</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3365992230389832</v>
+        <v>0.3364340154000717</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3605617202022888</v>
+        <v>0.3643245669871641</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2379682062940361</v>
+        <v>-0.2311207982889693</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2379682062940361</v>
+        <v>-0.2311207982889693</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3605617202022888</v>
+        <v>0.3643245669871641</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>2.55987451137947</v>
+        <v>4.582799712613659</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.55987451137947</v>
+        <v>4.582799712613659</v>
       </c>
     </row>
     <row r="13">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>3.434307874051561</v>
+        <v>6.084747855583996</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.434307874051561</v>
+        <v>6.084747855583996</v>
       </c>
     </row>
     <row r="19">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>2.766953864951772</v>
+        <v>4.902360887174315</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.766953864951772</v>
+        <v>4.902360887174315</v>
       </c>
     </row>
     <row r="36">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>3.254462363758577</v>
+        <v>5.766105898245254</v>
       </c>
       <c r="AB45" t="n">
-        <v>3.254462363758577</v>
+        <v>5.766105898245254</v>
       </c>
     </row>
     <row r="46">
@@ -4479,10 +4479,10 @@
         </is>
       </c>
       <c r="AA47" t="n">
-        <v>4.271171166281338</v>
+        <v>7.567463532092283</v>
       </c>
       <c r="AB47" t="n">
-        <v>4.271171166281338</v>
+        <v>7.567463532092283</v>
       </c>
     </row>
   </sheetData>
